--- a/Customer_Payment_zoho.xlsx
+++ b/Customer_Payment_zoho.xlsx
@@ -86,7 +86,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y720"/>
+  <dimension ref="A1:Y736"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.53125" customWidth="true"/>
@@ -84467,6 +84467,1878 @@
         <v>46253.0</v>
       </c>
     </row>
+    <row r="721">
+      <c r="A721" s="2" t="inlineStr">
+        <is>
+          <t>FS714</t>
+        </is>
+      </c>
+      <c r="B721" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508023</t>
+        </is>
+      </c>
+      <c r="C721" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D721" s="2" t="inlineStr">
+        <is>
+          <t>510492000001474001</t>
+        </is>
+      </c>
+      <c r="E721" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F721" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G721" s="2" t="inlineStr">
+        <is>
+          <t>270.000</t>
+        </is>
+      </c>
+      <c r="H721" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I721" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J721" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K721" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L721" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M721" s="2" t="inlineStr">
+        <is>
+          <t>714</t>
+        </is>
+      </c>
+      <c r="N721" s="2" t="inlineStr">
+        <is>
+          <t>First Class Learning Reading Central</t>
+        </is>
+      </c>
+      <c r="O721" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P721" s="5" t="n">
+        <v>46261.0</v>
+      </c>
+      <c r="Q721" s="6" t="n">
+        <v>46274.65425925926</v>
+      </c>
+      <c r="R721" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S721" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T721" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508027</t>
+        </is>
+      </c>
+      <c r="U721" s="2" t="n">
+        <v>270.0</v>
+      </c>
+      <c r="V721" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W721" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X721" s="2" t="inlineStr">
+        <is>
+          <t>242080</t>
+        </is>
+      </c>
+      <c r="Y721" s="5" t="n">
+        <v>46261.0</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="2" t="inlineStr">
+        <is>
+          <t>FS715</t>
+        </is>
+      </c>
+      <c r="B722" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508040</t>
+        </is>
+      </c>
+      <c r="C722" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D722" s="2" t="inlineStr">
+        <is>
+          <t>510492000000541229</t>
+        </is>
+      </c>
+      <c r="E722" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F722" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G722" s="2" t="inlineStr">
+        <is>
+          <t>120.000</t>
+        </is>
+      </c>
+      <c r="H722" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I722" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J722" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K722" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L722" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M722" s="2" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="N722" s="2" t="inlineStr">
+        <is>
+          <t>Optimum Global Care</t>
+        </is>
+      </c>
+      <c r="O722" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P722" s="5" t="n">
+        <v>46261.0</v>
+      </c>
+      <c r="Q722" s="6" t="n">
+        <v>46274.65491898148</v>
+      </c>
+      <c r="R722" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S722" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T722" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508044</t>
+        </is>
+      </c>
+      <c r="U722" s="2" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="V722" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W722" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X722" s="2" t="inlineStr">
+        <is>
+          <t>242081</t>
+        </is>
+      </c>
+      <c r="Y722" s="5" t="n">
+        <v>46261.0</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="2" t="inlineStr">
+        <is>
+          <t>FS716</t>
+        </is>
+      </c>
+      <c r="B723" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508057</t>
+        </is>
+      </c>
+      <c r="C723" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D723" s="2" t="inlineStr">
+        <is>
+          <t>510492000001488006</t>
+        </is>
+      </c>
+      <c r="E723" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F723" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G723" s="2" t="inlineStr">
+        <is>
+          <t>80.000</t>
+        </is>
+      </c>
+      <c r="H723" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I723" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J723" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K723" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L723" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M723" s="2" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="N723" s="2" t="inlineStr">
+        <is>
+          <t>SPOT CLEANERS LTD</t>
+        </is>
+      </c>
+      <c r="O723" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P723" s="5" t="n">
+        <v>46266.0</v>
+      </c>
+      <c r="Q723" s="6" t="n">
+        <v>46274.655543981484</v>
+      </c>
+      <c r="R723" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S723" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T723" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508061</t>
+        </is>
+      </c>
+      <c r="U723" s="2" t="n">
+        <v>80.0</v>
+      </c>
+      <c r="V723" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W723" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X723" s="2" t="inlineStr">
+        <is>
+          <t>242084</t>
+        </is>
+      </c>
+      <c r="Y723" s="5" t="n">
+        <v>46265.0</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="2" t="inlineStr">
+        <is>
+          <t>FS717</t>
+        </is>
+      </c>
+      <c r="B724" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508074</t>
+        </is>
+      </c>
+      <c r="C724" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D724" s="2" t="inlineStr">
+        <is>
+          <t>510492000000327139</t>
+        </is>
+      </c>
+      <c r="E724" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F724" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G724" s="2" t="inlineStr">
+        <is>
+          <t>400.000</t>
+        </is>
+      </c>
+      <c r="H724" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I724" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J724" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K724" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L724" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M724" s="2" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="N724" s="2" t="inlineStr">
+        <is>
+          <t>BATHROOMS LONDON LIMITED</t>
+        </is>
+      </c>
+      <c r="O724" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P724" s="5" t="n">
+        <v>46266.0</v>
+      </c>
+      <c r="Q724" s="6" t="n">
+        <v>46274.657858796294</v>
+      </c>
+      <c r="R724" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S724" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T724" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508078</t>
+        </is>
+      </c>
+      <c r="U724" s="2" t="n">
+        <v>400.0</v>
+      </c>
+      <c r="V724" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W724" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X724" s="2" t="inlineStr">
+        <is>
+          <t>242067</t>
+        </is>
+      </c>
+      <c r="Y724" s="5" t="n">
+        <v>46247.0</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="2" t="inlineStr">
+        <is>
+          <t>FS718</t>
+        </is>
+      </c>
+      <c r="B725" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508091</t>
+        </is>
+      </c>
+      <c r="C725" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D725" s="2" t="inlineStr">
+        <is>
+          <t>510492000000192073</t>
+        </is>
+      </c>
+      <c r="E725" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F725" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G725" s="2" t="inlineStr">
+        <is>
+          <t>238.800</t>
+        </is>
+      </c>
+      <c r="H725" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I725" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J725" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K725" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L725" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M725" s="2" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="N725" s="2" t="inlineStr">
+        <is>
+          <t>SUPERHOUSE (UK) LIMITED</t>
+        </is>
+      </c>
+      <c r="O725" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P725" s="5" t="n">
+        <v>46266.0</v>
+      </c>
+      <c r="Q725" s="6" t="n">
+        <v>46274.65850694444</v>
+      </c>
+      <c r="R725" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S725" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T725" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508095</t>
+        </is>
+      </c>
+      <c r="U725" s="2" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="V725" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W725" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X725" s="2" t="inlineStr">
+        <is>
+          <t>241789</t>
+        </is>
+      </c>
+      <c r="Y725" s="5" t="n">
+        <v>46054.0</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="2" t="inlineStr">
+        <is>
+          <t>FS719</t>
+        </is>
+      </c>
+      <c r="B726" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508108</t>
+        </is>
+      </c>
+      <c r="C726" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D726" s="2" t="inlineStr">
+        <is>
+          <t>510492000000192073</t>
+        </is>
+      </c>
+      <c r="E726" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F726" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G726" s="2" t="inlineStr">
+        <is>
+          <t>238.800</t>
+        </is>
+      </c>
+      <c r="H726" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I726" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J726" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K726" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L726" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M726" s="2" t="inlineStr">
+        <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="N726" s="2" t="inlineStr">
+        <is>
+          <t>SUPERHOUSE (UK) LIMITED</t>
+        </is>
+      </c>
+      <c r="O726" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P726" s="5" t="n">
+        <v>46266.0</v>
+      </c>
+      <c r="Q726" s="6" t="n">
+        <v>46274.65871527778</v>
+      </c>
+      <c r="R726" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S726" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T726" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508112</t>
+        </is>
+      </c>
+      <c r="U726" s="2" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="V726" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W726" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X726" s="2" t="inlineStr">
+        <is>
+          <t>241835</t>
+        </is>
+      </c>
+      <c r="Y726" s="5" t="n">
+        <v>46082.0</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="2" t="inlineStr">
+        <is>
+          <t>FS720</t>
+        </is>
+      </c>
+      <c r="B727" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508125</t>
+        </is>
+      </c>
+      <c r="C727" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D727" s="2" t="inlineStr">
+        <is>
+          <t>510492000000560319</t>
+        </is>
+      </c>
+      <c r="E727" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F727" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G727" s="2" t="inlineStr">
+        <is>
+          <t>375.000</t>
+        </is>
+      </c>
+      <c r="H727" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I727" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J727" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K727" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L727" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M727" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="N727" s="2" t="inlineStr">
+        <is>
+          <t>RRJ Carpentry and Joinery Ltd</t>
+        </is>
+      </c>
+      <c r="O727" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P727" s="5" t="n">
+        <v>46266.0</v>
+      </c>
+      <c r="Q727" s="6" t="n">
+        <v>46274.659270833334</v>
+      </c>
+      <c r="R727" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S727" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T727" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508129</t>
+        </is>
+      </c>
+      <c r="U727" s="2" t="n">
+        <v>375.0</v>
+      </c>
+      <c r="V727" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W727" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X727" s="2" t="inlineStr">
+        <is>
+          <t>241823</t>
+        </is>
+      </c>
+      <c r="Y727" s="5" t="n">
+        <v>46070.0</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="2" t="inlineStr">
+        <is>
+          <t>FS721</t>
+        </is>
+      </c>
+      <c r="B728" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508142</t>
+        </is>
+      </c>
+      <c r="C728" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D728" s="2" t="inlineStr">
+        <is>
+          <t>510492000000560319</t>
+        </is>
+      </c>
+      <c r="E728" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F728" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G728" s="2" t="inlineStr">
+        <is>
+          <t>240.000</t>
+        </is>
+      </c>
+      <c r="H728" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I728" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J728" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K728" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L728" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M728" s="2" t="inlineStr">
+        <is>
+          <t>721</t>
+        </is>
+      </c>
+      <c r="N728" s="2" t="inlineStr">
+        <is>
+          <t>RRJ Carpentry and Joinery Ltd</t>
+        </is>
+      </c>
+      <c r="O728" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P728" s="5" t="n">
+        <v>46266.0</v>
+      </c>
+      <c r="Q728" s="6" t="n">
+        <v>46274.659780092596</v>
+      </c>
+      <c r="R728" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S728" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T728" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508146</t>
+        </is>
+      </c>
+      <c r="U728" s="2" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="V728" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W728" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X728" s="2" t="inlineStr">
+        <is>
+          <t>241858</t>
+        </is>
+      </c>
+      <c r="Y728" s="5" t="n">
+        <v>46084.0</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="2" t="inlineStr">
+        <is>
+          <t>FS722</t>
+        </is>
+      </c>
+      <c r="B729" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508159</t>
+        </is>
+      </c>
+      <c r="C729" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D729" s="2" t="inlineStr">
+        <is>
+          <t>510492000000560319</t>
+        </is>
+      </c>
+      <c r="E729" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F729" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G729" s="2" t="inlineStr">
+        <is>
+          <t>240.000</t>
+        </is>
+      </c>
+      <c r="H729" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I729" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J729" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K729" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L729" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M729" s="2" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="N729" s="2" t="inlineStr">
+        <is>
+          <t>RRJ Carpentry and Joinery Ltd</t>
+        </is>
+      </c>
+      <c r="O729" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P729" s="5" t="n">
+        <v>46266.0</v>
+      </c>
+      <c r="Q729" s="6" t="n">
+        <v>46274.65998842593</v>
+      </c>
+      <c r="R729" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S729" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T729" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508163</t>
+        </is>
+      </c>
+      <c r="U729" s="2" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="V729" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W729" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X729" s="2" t="inlineStr">
+        <is>
+          <t>241889</t>
+        </is>
+      </c>
+      <c r="Y729" s="5" t="n">
+        <v>46113.0</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="2" t="inlineStr">
+        <is>
+          <t>FS723</t>
+        </is>
+      </c>
+      <c r="B730" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508176</t>
+        </is>
+      </c>
+      <c r="C730" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D730" s="2" t="inlineStr">
+        <is>
+          <t>510492000000505059</t>
+        </is>
+      </c>
+      <c r="E730" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F730" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G730" s="2" t="inlineStr">
+        <is>
+          <t>120.000</t>
+        </is>
+      </c>
+      <c r="H730" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I730" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J730" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K730" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L730" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M730" s="2" t="inlineStr">
+        <is>
+          <t>723</t>
+        </is>
+      </c>
+      <c r="N730" s="2" t="inlineStr">
+        <is>
+          <t>Chorus Music Therapy &amp; Education</t>
+        </is>
+      </c>
+      <c r="O730" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P730" s="5" t="n">
+        <v>46266.0</v>
+      </c>
+      <c r="Q730" s="6" t="n">
+        <v>46274.66025462963</v>
+      </c>
+      <c r="R730" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S730" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T730" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508180</t>
+        </is>
+      </c>
+      <c r="U730" s="2" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="V730" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W730" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X730" s="2" t="inlineStr">
+        <is>
+          <t>242042</t>
+        </is>
+      </c>
+      <c r="Y730" s="5" t="n">
+        <v>46235.0</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="2" t="inlineStr">
+        <is>
+          <t>FS724</t>
+        </is>
+      </c>
+      <c r="B731" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508193</t>
+        </is>
+      </c>
+      <c r="C731" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D731" s="2" t="inlineStr">
+        <is>
+          <t>510492000001057001</t>
+        </is>
+      </c>
+      <c r="E731" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F731" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G731" s="2" t="inlineStr">
+        <is>
+          <t>500.000</t>
+        </is>
+      </c>
+      <c r="H731" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I731" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J731" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K731" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L731" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M731" s="2" t="inlineStr">
+        <is>
+          <t>724</t>
+        </is>
+      </c>
+      <c r="N731" s="2" t="inlineStr">
+        <is>
+          <t>Corby Motors Ltd</t>
+        </is>
+      </c>
+      <c r="O731" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P731" s="5" t="n">
+        <v>46267.0</v>
+      </c>
+      <c r="Q731" s="6" t="n">
+        <v>46274.6606712963</v>
+      </c>
+      <c r="R731" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S731" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T731" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508197</t>
+        </is>
+      </c>
+      <c r="U731" s="2" t="n">
+        <v>500.0</v>
+      </c>
+      <c r="V731" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W731" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X731" s="2" t="inlineStr">
+        <is>
+          <t>242082</t>
+        </is>
+      </c>
+      <c r="Y731" s="5" t="n">
+        <v>46263.0</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="2" t="inlineStr">
+        <is>
+          <t>FS725</t>
+        </is>
+      </c>
+      <c r="B732" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508210</t>
+        </is>
+      </c>
+      <c r="C732" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D732" s="2" t="inlineStr">
+        <is>
+          <t>510492000000946037</t>
+        </is>
+      </c>
+      <c r="E732" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F732" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G732" s="2" t="inlineStr">
+        <is>
+          <t>450.000</t>
+        </is>
+      </c>
+      <c r="H732" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I732" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J732" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K732" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L732" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M732" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="N732" s="2" t="inlineStr">
+        <is>
+          <t>Ace Learning Plus Limited</t>
+        </is>
+      </c>
+      <c r="O732" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P732" s="5" t="n">
+        <v>46267.0</v>
+      </c>
+      <c r="Q732" s="6" t="n">
+        <v>46274.66107638889</v>
+      </c>
+      <c r="R732" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S732" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T732" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508214</t>
+        </is>
+      </c>
+      <c r="U732" s="2" t="n">
+        <v>450.0</v>
+      </c>
+      <c r="V732" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W732" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X732" s="2" t="inlineStr">
+        <is>
+          <t>242015</t>
+        </is>
+      </c>
+      <c r="Y732" s="5" t="n">
+        <v>46213.0</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="2" t="inlineStr">
+        <is>
+          <t>FS726</t>
+        </is>
+      </c>
+      <c r="B733" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508227</t>
+        </is>
+      </c>
+      <c r="C733" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D733" s="2" t="inlineStr">
+        <is>
+          <t>510492000001155001</t>
+        </is>
+      </c>
+      <c r="E733" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F733" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G733" s="2" t="inlineStr">
+        <is>
+          <t>360.000</t>
+        </is>
+      </c>
+      <c r="H733" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I733" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J733" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K733" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L733" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M733" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="N733" s="2" t="inlineStr">
+        <is>
+          <t>Galloway Pest Control</t>
+        </is>
+      </c>
+      <c r="O733" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P733" s="5" t="n">
+        <v>46267.0</v>
+      </c>
+      <c r="Q733" s="6" t="n">
+        <v>46274.66142361111</v>
+      </c>
+      <c r="R733" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S733" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T733" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508231</t>
+        </is>
+      </c>
+      <c r="U733" s="2" t="n">
+        <v>360.0</v>
+      </c>
+      <c r="V733" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W733" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X733" s="2" t="inlineStr">
+        <is>
+          <t>242113</t>
+        </is>
+      </c>
+      <c r="Y733" s="5" t="n">
+        <v>46266.0</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="2" t="inlineStr">
+        <is>
+          <t>FS727</t>
+        </is>
+      </c>
+      <c r="B734" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508244</t>
+        </is>
+      </c>
+      <c r="C734" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D734" s="2" t="inlineStr">
+        <is>
+          <t>510492000000822033</t>
+        </is>
+      </c>
+      <c r="E734" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F734" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G734" s="2" t="inlineStr">
+        <is>
+          <t>420.000</t>
+        </is>
+      </c>
+      <c r="H734" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I734" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J734" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K734" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L734" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M734" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="N734" s="2" t="inlineStr">
+        <is>
+          <t>Sofiya Designs Limited</t>
+        </is>
+      </c>
+      <c r="O734" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P734" s="5" t="n">
+        <v>46268.0</v>
+      </c>
+      <c r="Q734" s="6" t="n">
+        <v>46274.66179398148</v>
+      </c>
+      <c r="R734" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S734" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T734" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508248</t>
+        </is>
+      </c>
+      <c r="U734" s="2" t="n">
+        <v>420.0</v>
+      </c>
+      <c r="V734" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W734" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X734" s="2" t="inlineStr">
+        <is>
+          <t>242112</t>
+        </is>
+      </c>
+      <c r="Y734" s="5" t="n">
+        <v>46267.0</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="2" t="inlineStr">
+        <is>
+          <t>FS728</t>
+        </is>
+      </c>
+      <c r="B735" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508261</t>
+        </is>
+      </c>
+      <c r="C735" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D735" s="2" t="inlineStr">
+        <is>
+          <t>510492000001488006</t>
+        </is>
+      </c>
+      <c r="E735" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F735" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G735" s="2" t="inlineStr">
+        <is>
+          <t>50.000</t>
+        </is>
+      </c>
+      <c r="H735" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I735" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J735" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K735" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L735" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M735" s="2" t="inlineStr">
+        <is>
+          <t>728</t>
+        </is>
+      </c>
+      <c r="N735" s="2" t="inlineStr">
+        <is>
+          <t>SPOT CLEANERS LTD</t>
+        </is>
+      </c>
+      <c r="O735" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P735" s="5" t="n">
+        <v>46269.0</v>
+      </c>
+      <c r="Q735" s="6" t="n">
+        <v>46274.66216435185</v>
+      </c>
+      <c r="R735" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S735" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T735" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508265</t>
+        </is>
+      </c>
+      <c r="U735" s="2" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="V735" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W735" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X735" s="2" t="inlineStr">
+        <is>
+          <t>242084</t>
+        </is>
+      </c>
+      <c r="Y735" s="5" t="n">
+        <v>46265.0</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="2" t="inlineStr">
+        <is>
+          <t>FS729</t>
+        </is>
+      </c>
+      <c r="B736" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508278</t>
+        </is>
+      </c>
+      <c r="C736" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D736" s="2" t="inlineStr">
+        <is>
+          <t>510492000000742001</t>
+        </is>
+      </c>
+      <c r="E736" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F736" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G736" s="2" t="inlineStr">
+        <is>
+          <t>240.000</t>
+        </is>
+      </c>
+      <c r="H736" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I736" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J736" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K736" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L736" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M736" s="2" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="N736" s="2" t="inlineStr">
+        <is>
+          <t>Adam’s Painting and Decorating</t>
+        </is>
+      </c>
+      <c r="O736" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P736" s="5" t="n">
+        <v>46273.0</v>
+      </c>
+      <c r="Q736" s="6" t="n">
+        <v>46274.662511574075</v>
+      </c>
+      <c r="R736" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S736" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T736" s="2" t="inlineStr">
+        <is>
+          <t>510492000001508282</t>
+        </is>
+      </c>
+      <c r="U736" s="2" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="V736" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W736" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X736" s="2" t="inlineStr">
+        <is>
+          <t>242099</t>
+        </is>
+      </c>
+      <c r="Y736" s="5" t="n">
+        <v>46266.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Customer_Payment_zoho.xlsx
+++ b/Customer_Payment_zoho.xlsx
@@ -86,7 +86,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y736"/>
+  <dimension ref="A1:Y737"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.53125" customWidth="true"/>
@@ -86339,6 +86339,123 @@
         <v>46266.0</v>
       </c>
     </row>
+    <row r="737">
+      <c r="A737" s="2" t="inlineStr">
+        <is>
+          <t>FS730</t>
+        </is>
+      </c>
+      <c r="B737" s="2" t="inlineStr">
+        <is>
+          <t>510492000001510026</t>
+        </is>
+      </c>
+      <c r="C737" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D737" s="2" t="inlineStr">
+        <is>
+          <t>510492000001324001</t>
+        </is>
+      </c>
+      <c r="E737" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F737" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G737" s="2" t="inlineStr">
+        <is>
+          <t>1000.000</t>
+        </is>
+      </c>
+      <c r="H737" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I737" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J737" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K737" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L737" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M737" s="2" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="N737" s="2" t="inlineStr">
+        <is>
+          <t>READING PROPERTIES GROUP LTD</t>
+        </is>
+      </c>
+      <c r="O737" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P737" s="5" t="n">
+        <v>46266.0</v>
+      </c>
+      <c r="Q737" s="6" t="n">
+        <v>46275.62856481481</v>
+      </c>
+      <c r="R737" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S737" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T737" s="2" t="inlineStr">
+        <is>
+          <t>510492000001510030</t>
+        </is>
+      </c>
+      <c r="U737" s="2" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="V737" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W737" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X737" s="2" t="inlineStr">
+        <is>
+          <t>242117</t>
+        </is>
+      </c>
+      <c r="Y737" s="5" t="n">
+        <v>46266.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Customer_Payment_zoho.xlsx
+++ b/Customer_Payment_zoho.xlsx
@@ -86,7 +86,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y737"/>
+  <dimension ref="A1:Y738"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.53125" customWidth="true"/>
@@ -86456,6 +86456,123 @@
         <v>46266.0</v>
       </c>
     </row>
+    <row r="738">
+      <c r="A738" s="2" t="inlineStr">
+        <is>
+          <t>FS731</t>
+        </is>
+      </c>
+      <c r="B738" s="2" t="inlineStr">
+        <is>
+          <t>510492000001525002</t>
+        </is>
+      </c>
+      <c r="C738" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D738" s="2" t="inlineStr">
+        <is>
+          <t>510492000000970001</t>
+        </is>
+      </c>
+      <c r="E738" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F738" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G738" s="2" t="inlineStr">
+        <is>
+          <t>1000.000</t>
+        </is>
+      </c>
+      <c r="H738" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I738" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J738" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K738" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L738" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M738" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="N738" s="2" t="inlineStr">
+        <is>
+          <t>Superhouse Education Foundation</t>
+        </is>
+      </c>
+      <c r="O738" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P738" s="5" t="n">
+        <v>46279.0</v>
+      </c>
+      <c r="Q738" s="6" t="n">
+        <v>46281.659791666665</v>
+      </c>
+      <c r="R738" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S738" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T738" s="2" t="inlineStr">
+        <is>
+          <t>510492000001525006</t>
+        </is>
+      </c>
+      <c r="U738" s="2" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="V738" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W738" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X738" s="2" t="inlineStr">
+        <is>
+          <t>242060</t>
+        </is>
+      </c>
+      <c r="Y738" s="5" t="n">
+        <v>46239.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Customer_Payment_zoho.xlsx
+++ b/Customer_Payment_zoho.xlsx
@@ -86,7 +86,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y738"/>
+  <dimension ref="A1:Y749"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.53125" customWidth="true"/>
@@ -86573,6 +86573,1293 @@
         <v>46239.0</v>
       </c>
     </row>
+    <row r="739">
+      <c r="A739" s="2" t="inlineStr">
+        <is>
+          <t>FS732</t>
+        </is>
+      </c>
+      <c r="B739" s="2" t="inlineStr">
+        <is>
+          <t>510492000001531002</t>
+        </is>
+      </c>
+      <c r="C739" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D739" s="2" t="inlineStr">
+        <is>
+          <t>510492000001506003</t>
+        </is>
+      </c>
+      <c r="E739" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F739" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G739" s="2" t="inlineStr">
+        <is>
+          <t>300.000</t>
+        </is>
+      </c>
+      <c r="H739" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I739" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J739" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K739" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L739" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M739" s="2" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="N739" s="2" t="inlineStr">
+        <is>
+          <t>Mrs. Almina Dhalla</t>
+        </is>
+      </c>
+      <c r="O739" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P739" s="5" t="n">
+        <v>46274.0</v>
+      </c>
+      <c r="Q739" s="6" t="n">
+        <v>46283.53625</v>
+      </c>
+      <c r="R739" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S739" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T739" s="2" t="inlineStr">
+        <is>
+          <t>510492000001531006</t>
+        </is>
+      </c>
+      <c r="U739" s="2" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="V739" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W739" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X739" s="2" t="inlineStr">
+        <is>
+          <t>242115</t>
+        </is>
+      </c>
+      <c r="Y739" s="5" t="n">
+        <v>46272.0</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="2" t="inlineStr">
+        <is>
+          <t>FS733</t>
+        </is>
+      </c>
+      <c r="B740" s="2" t="inlineStr">
+        <is>
+          <t>510492000001531019</t>
+        </is>
+      </c>
+      <c r="C740" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D740" s="2" t="inlineStr">
+        <is>
+          <t>510492000001025001</t>
+        </is>
+      </c>
+      <c r="E740" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F740" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G740" s="2" t="inlineStr">
+        <is>
+          <t>103.450</t>
+        </is>
+      </c>
+      <c r="H740" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I740" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J740" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K740" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L740" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M740" s="2" t="inlineStr">
+        <is>
+          <t>733</t>
+        </is>
+      </c>
+      <c r="N740" s="2" t="inlineStr">
+        <is>
+          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
+        </is>
+      </c>
+      <c r="O740" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P740" s="5" t="n">
+        <v>46275.0</v>
+      </c>
+      <c r="Q740" s="6" t="n">
+        <v>46283.537083333336</v>
+      </c>
+      <c r="R740" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S740" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T740" s="2" t="inlineStr">
+        <is>
+          <t>510492000001531023</t>
+        </is>
+      </c>
+      <c r="U740" s="2" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="V740" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W740" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X740" s="2" t="inlineStr">
+        <is>
+          <t>242017</t>
+        </is>
+      </c>
+      <c r="Y740" s="5" t="n">
+        <v>46266.0</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="2" t="inlineStr">
+        <is>
+          <t>FS734</t>
+        </is>
+      </c>
+      <c r="B741" s="2" t="inlineStr">
+        <is>
+          <t>510492000001531036</t>
+        </is>
+      </c>
+      <c r="C741" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D741" s="2" t="inlineStr">
+        <is>
+          <t>510492000001025001</t>
+        </is>
+      </c>
+      <c r="E741" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F741" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G741" s="2" t="inlineStr">
+        <is>
+          <t>103.450</t>
+        </is>
+      </c>
+      <c r="H741" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I741" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J741" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K741" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L741" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M741" s="2" t="inlineStr">
+        <is>
+          <t>734</t>
+        </is>
+      </c>
+      <c r="N741" s="2" t="inlineStr">
+        <is>
+          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
+        </is>
+      </c>
+      <c r="O741" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P741" s="5" t="n">
+        <v>46275.0</v>
+      </c>
+      <c r="Q741" s="6" t="n">
+        <v>46283.53728009259</v>
+      </c>
+      <c r="R741" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S741" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T741" s="2" t="inlineStr">
+        <is>
+          <t>510492000001531040</t>
+        </is>
+      </c>
+      <c r="U741" s="2" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="V741" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W741" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X741" s="2" t="inlineStr">
+        <is>
+          <t>242017</t>
+        </is>
+      </c>
+      <c r="Y741" s="5" t="n">
+        <v>46266.0</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="2" t="inlineStr">
+        <is>
+          <t>FS735</t>
+        </is>
+      </c>
+      <c r="B742" s="2" t="inlineStr">
+        <is>
+          <t>510492000001531053</t>
+        </is>
+      </c>
+      <c r="C742" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D742" s="2" t="inlineStr">
+        <is>
+          <t>510492000000122647</t>
+        </is>
+      </c>
+      <c r="E742" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F742" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G742" s="2" t="inlineStr">
+        <is>
+          <t>238.800</t>
+        </is>
+      </c>
+      <c r="H742" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I742" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J742" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K742" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L742" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M742" s="2" t="inlineStr">
+        <is>
+          <t>735</t>
+        </is>
+      </c>
+      <c r="N742" s="2" t="inlineStr">
+        <is>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+        </is>
+      </c>
+      <c r="O742" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P742" s="5" t="n">
+        <v>46276.0</v>
+      </c>
+      <c r="Q742" s="6" t="n">
+        <v>46283.53769675926</v>
+      </c>
+      <c r="R742" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S742" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T742" s="2" t="inlineStr">
+        <is>
+          <t>510492000001531057</t>
+        </is>
+      </c>
+      <c r="U742" s="2" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="V742" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W742" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X742" s="2" t="inlineStr">
+        <is>
+          <t>241984</t>
+        </is>
+      </c>
+      <c r="Y742" s="5" t="n">
+        <v>46204.0</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="2" t="inlineStr">
+        <is>
+          <t>FS736</t>
+        </is>
+      </c>
+      <c r="B743" s="2" t="inlineStr">
+        <is>
+          <t>510492000001531070</t>
+        </is>
+      </c>
+      <c r="C743" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D743" s="2" t="inlineStr">
+        <is>
+          <t>510492000001025001</t>
+        </is>
+      </c>
+      <c r="E743" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F743" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G743" s="2" t="inlineStr">
+        <is>
+          <t>103.400</t>
+        </is>
+      </c>
+      <c r="H743" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I743" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J743" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K743" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L743" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M743" s="2" t="inlineStr">
+        <is>
+          <t>736</t>
+        </is>
+      </c>
+      <c r="N743" s="2" t="inlineStr">
+        <is>
+          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
+        </is>
+      </c>
+      <c r="O743" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P743" s="5" t="n">
+        <v>46276.0</v>
+      </c>
+      <c r="Q743" s="6" t="n">
+        <v>46283.5381712963</v>
+      </c>
+      <c r="R743" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S743" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T743" s="2" t="inlineStr">
+        <is>
+          <t>510492000001531074</t>
+        </is>
+      </c>
+      <c r="U743" s="2" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="V743" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W743" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X743" s="2" t="inlineStr">
+        <is>
+          <t>242017</t>
+        </is>
+      </c>
+      <c r="Y743" s="5" t="n">
+        <v>46266.0</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="2" t="inlineStr">
+        <is>
+          <t>FS737</t>
+        </is>
+      </c>
+      <c r="B744" s="2" t="inlineStr">
+        <is>
+          <t>510492000001531087</t>
+        </is>
+      </c>
+      <c r="C744" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D744" s="2" t="inlineStr">
+        <is>
+          <t>510492000001517001</t>
+        </is>
+      </c>
+      <c r="E744" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F744" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G744" s="2" t="inlineStr">
+        <is>
+          <t>10.000</t>
+        </is>
+      </c>
+      <c r="H744" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I744" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J744" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K744" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L744" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M744" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="N744" s="2" t="inlineStr">
+        <is>
+          <t>Max Out Tutoring</t>
+        </is>
+      </c>
+      <c r="O744" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P744" s="5" t="n">
+        <v>46279.0</v>
+      </c>
+      <c r="Q744" s="6" t="n">
+        <v>46283.53868055555</v>
+      </c>
+      <c r="R744" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S744" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T744" s="2" t="inlineStr">
+        <is>
+          <t>510492000001531091</t>
+        </is>
+      </c>
+      <c r="U744" s="2" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="V744" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W744" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X744" s="2" t="inlineStr">
+        <is>
+          <t>242120</t>
+        </is>
+      </c>
+      <c r="Y744" s="5" t="n">
+        <v>46277.0</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="2" t="inlineStr">
+        <is>
+          <t>FS738</t>
+        </is>
+      </c>
+      <c r="B745" s="2" t="inlineStr">
+        <is>
+          <t>510492000001531104</t>
+        </is>
+      </c>
+      <c r="C745" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D745" s="2" t="inlineStr">
+        <is>
+          <t>510492000001378001</t>
+        </is>
+      </c>
+      <c r="E745" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F745" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G745" s="2" t="inlineStr">
+        <is>
+          <t>540.000</t>
+        </is>
+      </c>
+      <c r="H745" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I745" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J745" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K745" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L745" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M745" s="2" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="N745" s="2" t="inlineStr">
+        <is>
+          <t>ALTAI MOUNTAIN SHILAJIT LTD</t>
+        </is>
+      </c>
+      <c r="O745" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P745" s="5" t="n">
+        <v>46279.0</v>
+      </c>
+      <c r="Q745" s="6" t="n">
+        <v>46283.538993055554</v>
+      </c>
+      <c r="R745" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S745" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T745" s="2" t="inlineStr">
+        <is>
+          <t>510492000001531108</t>
+        </is>
+      </c>
+      <c r="U745" s="2" t="n">
+        <v>540.0</v>
+      </c>
+      <c r="V745" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W745" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X745" s="2" t="inlineStr">
+        <is>
+          <t>242119</t>
+        </is>
+      </c>
+      <c r="Y745" s="5" t="n">
+        <v>46276.0</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="2" t="inlineStr">
+        <is>
+          <t>FS739</t>
+        </is>
+      </c>
+      <c r="B746" s="2" t="inlineStr">
+        <is>
+          <t>510492000001531121</t>
+        </is>
+      </c>
+      <c r="C746" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D746" s="2" t="inlineStr">
+        <is>
+          <t>510492000001517001</t>
+        </is>
+      </c>
+      <c r="E746" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F746" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G746" s="2" t="inlineStr">
+        <is>
+          <t>350.000</t>
+        </is>
+      </c>
+      <c r="H746" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I746" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J746" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K746" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L746" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M746" s="2" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="N746" s="2" t="inlineStr">
+        <is>
+          <t>Max Out Tutoring</t>
+        </is>
+      </c>
+      <c r="O746" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P746" s="5" t="n">
+        <v>46280.0</v>
+      </c>
+      <c r="Q746" s="6" t="n">
+        <v>46283.539375</v>
+      </c>
+      <c r="R746" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S746" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T746" s="2" t="inlineStr">
+        <is>
+          <t>510492000001531125</t>
+        </is>
+      </c>
+      <c r="U746" s="2" t="n">
+        <v>350.0</v>
+      </c>
+      <c r="V746" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W746" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X746" s="2" t="inlineStr">
+        <is>
+          <t>242120</t>
+        </is>
+      </c>
+      <c r="Y746" s="5" t="n">
+        <v>46277.0</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="2" t="inlineStr">
+        <is>
+          <t>FS740</t>
+        </is>
+      </c>
+      <c r="B747" s="2" t="inlineStr">
+        <is>
+          <t>510492000001531138</t>
+        </is>
+      </c>
+      <c r="C747" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D747" s="2" t="inlineStr">
+        <is>
+          <t>510492000001025001</t>
+        </is>
+      </c>
+      <c r="E747" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F747" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G747" s="2" t="inlineStr">
+        <is>
+          <t>125.000</t>
+        </is>
+      </c>
+      <c r="H747" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I747" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J747" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K747" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L747" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M747" s="2" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="N747" s="2" t="inlineStr">
+        <is>
+          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
+        </is>
+      </c>
+      <c r="O747" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P747" s="5" t="n">
+        <v>46281.0</v>
+      </c>
+      <c r="Q747" s="6" t="n">
+        <v>46283.54048611111</v>
+      </c>
+      <c r="R747" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S747" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T747" s="2" t="inlineStr">
+        <is>
+          <t>510492000001531142</t>
+        </is>
+      </c>
+      <c r="U747" s="2" t="n">
+        <v>125.0</v>
+      </c>
+      <c r="V747" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W747" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X747" s="2" t="inlineStr">
+        <is>
+          <t>242127</t>
+        </is>
+      </c>
+      <c r="Y747" s="5" t="n">
+        <v>46280.0</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="2" t="inlineStr">
+        <is>
+          <t>FS741</t>
+        </is>
+      </c>
+      <c r="B748" s="2" t="inlineStr">
+        <is>
+          <t>510492000001531155</t>
+        </is>
+      </c>
+      <c r="C748" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D748" s="2" t="inlineStr">
+        <is>
+          <t>510492000001025001</t>
+        </is>
+      </c>
+      <c r="E748" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F748" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G748" s="2" t="inlineStr">
+        <is>
+          <t>125.000</t>
+        </is>
+      </c>
+      <c r="H748" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I748" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J748" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K748" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L748" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M748" s="2" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="N748" s="2" t="inlineStr">
+        <is>
+          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
+        </is>
+      </c>
+      <c r="O748" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P748" s="5" t="n">
+        <v>46281.0</v>
+      </c>
+      <c r="Q748" s="6" t="n">
+        <v>46283.54076388889</v>
+      </c>
+      <c r="R748" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S748" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T748" s="2" t="inlineStr">
+        <is>
+          <t>510492000001531159</t>
+        </is>
+      </c>
+      <c r="U748" s="2" t="n">
+        <v>125.0</v>
+      </c>
+      <c r="V748" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W748" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X748" s="2" t="inlineStr">
+        <is>
+          <t>242127</t>
+        </is>
+      </c>
+      <c r="Y748" s="5" t="n">
+        <v>46280.0</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="2" t="inlineStr">
+        <is>
+          <t>FS742</t>
+        </is>
+      </c>
+      <c r="B749" s="2" t="inlineStr">
+        <is>
+          <t>510492000001531172</t>
+        </is>
+      </c>
+      <c r="C749" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D749" s="2" t="inlineStr">
+        <is>
+          <t>510492000001391001</t>
+        </is>
+      </c>
+      <c r="E749" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F749" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G749" s="2" t="inlineStr">
+        <is>
+          <t>18.960</t>
+        </is>
+      </c>
+      <c r="H749" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I749" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J749" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K749" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L749" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M749" s="2" t="inlineStr">
+        <is>
+          <t>742</t>
+        </is>
+      </c>
+      <c r="N749" s="2" t="inlineStr">
+        <is>
+          <t>PAVS DRIVING SCHOOL</t>
+        </is>
+      </c>
+      <c r="O749" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P749" s="5" t="n">
+        <v>46282.0</v>
+      </c>
+      <c r="Q749" s="6" t="n">
+        <v>46283.54108796296</v>
+      </c>
+      <c r="R749" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S749" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T749" s="2" t="inlineStr">
+        <is>
+          <t>510492000001531176</t>
+        </is>
+      </c>
+      <c r="U749" s="2" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="V749" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W749" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X749" s="2" t="inlineStr">
+        <is>
+          <t>242125</t>
+        </is>
+      </c>
+      <c r="Y749" s="5" t="n">
+        <v>46280.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Customer_Payment_zoho.xlsx
+++ b/Customer_Payment_zoho.xlsx
@@ -219,6 +219,7 @@
     <col min="128" max="128" width="19.53125" customWidth="true"/>
     <col min="129" max="129" width="19.53125" customWidth="true"/>
     <col min="130" max="130" width="19.53125" customWidth="true"/>
+    <col min="131" max="131" width="19.53125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/Customer_Payment_zoho.xlsx
+++ b/Customer_Payment_zoho.xlsx
@@ -86,7 +86,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y749"/>
+  <dimension ref="A1:Y755"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.53125" customWidth="true"/>
@@ -87861,6 +87861,708 @@
         <v>46280.0</v>
       </c>
     </row>
+    <row r="750">
+      <c r="A750" s="2" t="inlineStr">
+        <is>
+          <t>FS743</t>
+        </is>
+      </c>
+      <c r="B750" s="2" t="inlineStr">
+        <is>
+          <t>510492000001546014</t>
+        </is>
+      </c>
+      <c r="C750" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D750" s="2" t="inlineStr">
+        <is>
+          <t>510492000000256001</t>
+        </is>
+      </c>
+      <c r="E750" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F750" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G750" s="2" t="inlineStr">
+        <is>
+          <t>50.000</t>
+        </is>
+      </c>
+      <c r="H750" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I750" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J750" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K750" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L750" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M750" s="2" t="inlineStr">
+        <is>
+          <t>743</t>
+        </is>
+      </c>
+      <c r="N750" s="2" t="inlineStr">
+        <is>
+          <t>OPTIMUM GLOBAL LINKS</t>
+        </is>
+      </c>
+      <c r="O750" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P750" s="5" t="n">
+        <v>46283.0</v>
+      </c>
+      <c r="Q750" s="6" t="n">
+        <v>46290.427569444444</v>
+      </c>
+      <c r="R750" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S750" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T750" s="2" t="inlineStr">
+        <is>
+          <t>510492000001546018</t>
+        </is>
+      </c>
+      <c r="U750" s="2" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="V750" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W750" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X750" s="2" t="inlineStr">
+        <is>
+          <t>242128</t>
+        </is>
+      </c>
+      <c r="Y750" s="5" t="n">
+        <v>46282.0</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="2" t="inlineStr">
+        <is>
+          <t>FS744</t>
+        </is>
+      </c>
+      <c r="B751" s="2" t="inlineStr">
+        <is>
+          <t>510492000001546032</t>
+        </is>
+      </c>
+      <c r="C751" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D751" s="2" t="inlineStr">
+        <is>
+          <t>510492000001135181</t>
+        </is>
+      </c>
+      <c r="E751" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F751" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G751" s="2" t="inlineStr">
+        <is>
+          <t>150.000</t>
+        </is>
+      </c>
+      <c r="H751" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I751" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J751" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K751" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L751" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M751" s="2" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="N751" s="2" t="inlineStr">
+        <is>
+          <t>Greyson Studios</t>
+        </is>
+      </c>
+      <c r="O751" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P751" s="5" t="n">
+        <v>46283.0</v>
+      </c>
+      <c r="Q751" s="6" t="n">
+        <v>46290.427835648145</v>
+      </c>
+      <c r="R751" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S751" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T751" s="2" t="inlineStr">
+        <is>
+          <t>510492000001546036</t>
+        </is>
+      </c>
+      <c r="U751" s="2" t="n">
+        <v>150.0</v>
+      </c>
+      <c r="V751" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W751" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X751" s="2" t="inlineStr">
+        <is>
+          <t>241868</t>
+        </is>
+      </c>
+      <c r="Y751" s="5" t="n">
+        <v>46092.0</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="2" t="inlineStr">
+        <is>
+          <t>FS745</t>
+        </is>
+      </c>
+      <c r="B752" s="2" t="inlineStr">
+        <is>
+          <t>510492000001546050</t>
+        </is>
+      </c>
+      <c r="C752" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D752" s="2" t="inlineStr">
+        <is>
+          <t>510492000001531214</t>
+        </is>
+      </c>
+      <c r="E752" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F752" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G752" s="2" t="inlineStr">
+        <is>
+          <t>240.000</t>
+        </is>
+      </c>
+      <c r="H752" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I752" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J752" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K752" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L752" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M752" s="2" t="inlineStr">
+        <is>
+          <t>745</t>
+        </is>
+      </c>
+      <c r="N752" s="2" t="inlineStr">
+        <is>
+          <t>Kumon Harrow South</t>
+        </is>
+      </c>
+      <c r="O752" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P752" s="5" t="n">
+        <v>46286.0</v>
+      </c>
+      <c r="Q752" s="6" t="n">
+        <v>46290.42810185185</v>
+      </c>
+      <c r="R752" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S752" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T752" s="2" t="inlineStr">
+        <is>
+          <t>510492000001546054</t>
+        </is>
+      </c>
+      <c r="U752" s="2" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="V752" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W752" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X752" s="2" t="inlineStr">
+        <is>
+          <t>242130</t>
+        </is>
+      </c>
+      <c r="Y752" s="5" t="n">
+        <v>46283.0</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="2" t="inlineStr">
+        <is>
+          <t>FS746</t>
+        </is>
+      </c>
+      <c r="B753" s="2" t="inlineStr">
+        <is>
+          <t>510492000001546068</t>
+        </is>
+      </c>
+      <c r="C753" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D753" s="2" t="inlineStr">
+        <is>
+          <t>510492000001531188</t>
+        </is>
+      </c>
+      <c r="E753" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F753" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G753" s="2" t="inlineStr">
+        <is>
+          <t>240.000</t>
+        </is>
+      </c>
+      <c r="H753" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I753" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J753" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K753" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L753" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M753" s="2" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
+      <c r="N753" s="2" t="inlineStr">
+        <is>
+          <t>Kumon North Harrow</t>
+        </is>
+      </c>
+      <c r="O753" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P753" s="5" t="n">
+        <v>46286.0</v>
+      </c>
+      <c r="Q753" s="6" t="n">
+        <v>46290.42847222222</v>
+      </c>
+      <c r="R753" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S753" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T753" s="2" t="inlineStr">
+        <is>
+          <t>510492000001546072</t>
+        </is>
+      </c>
+      <c r="U753" s="2" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="V753" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W753" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X753" s="2" t="inlineStr">
+        <is>
+          <t>242129</t>
+        </is>
+      </c>
+      <c r="Y753" s="5" t="n">
+        <v>46283.0</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="2" t="inlineStr">
+        <is>
+          <t>FS747</t>
+        </is>
+      </c>
+      <c r="B754" s="2" t="inlineStr">
+        <is>
+          <t>510492000001546086</t>
+        </is>
+      </c>
+      <c r="C754" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D754" s="2" t="inlineStr">
+        <is>
+          <t>510492000001450146</t>
+        </is>
+      </c>
+      <c r="E754" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F754" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G754" s="2" t="inlineStr">
+        <is>
+          <t>120.000</t>
+        </is>
+      </c>
+      <c r="H754" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I754" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J754" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K754" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L754" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M754" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="N754" s="2" t="inlineStr">
+        <is>
+          <t>Mr. Phone Mobile &amp; Vape</t>
+        </is>
+      </c>
+      <c r="O754" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P754" s="5" t="n">
+        <v>46287.0</v>
+      </c>
+      <c r="Q754" s="6" t="n">
+        <v>46290.42885416667</v>
+      </c>
+      <c r="R754" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S754" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T754" s="2" t="inlineStr">
+        <is>
+          <t>510492000001546090</t>
+        </is>
+      </c>
+      <c r="U754" s="2" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="V754" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W754" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X754" s="2" t="inlineStr">
+        <is>
+          <t>242131</t>
+        </is>
+      </c>
+      <c r="Y754" s="5" t="n">
+        <v>46286.0</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="2" t="inlineStr">
+        <is>
+          <t>FS748</t>
+        </is>
+      </c>
+      <c r="B755" s="2" t="inlineStr">
+        <is>
+          <t>510492000001546104</t>
+        </is>
+      </c>
+      <c r="C755" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D755" s="2" t="inlineStr">
+        <is>
+          <t>510492000001488006</t>
+        </is>
+      </c>
+      <c r="E755" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F755" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G755" s="2" t="inlineStr">
+        <is>
+          <t>130.000</t>
+        </is>
+      </c>
+      <c r="H755" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I755" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J755" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K755" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L755" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M755" s="2" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="N755" s="2" t="inlineStr">
+        <is>
+          <t>SPOT CLEANERS LTD</t>
+        </is>
+      </c>
+      <c r="O755" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P755" s="5" t="n">
+        <v>46288.0</v>
+      </c>
+      <c r="Q755" s="6" t="n">
+        <v>46290.429131944446</v>
+      </c>
+      <c r="R755" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S755" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T755" s="2" t="inlineStr">
+        <is>
+          <t>510492000001546108</t>
+        </is>
+      </c>
+      <c r="U755" s="2" t="n">
+        <v>130.0</v>
+      </c>
+      <c r="V755" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W755" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X755" s="2" t="inlineStr">
+        <is>
+          <t>242118</t>
+        </is>
+      </c>
+      <c r="Y755" s="5" t="n">
+        <v>46275.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Customer_Payment_zoho.xlsx
+++ b/Customer_Payment_zoho.xlsx
@@ -86,7 +86,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y755"/>
+  <dimension ref="A1:Y765"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.53125" customWidth="true"/>
@@ -88563,6 +88563,1176 @@
         <v>46275.0</v>
       </c>
     </row>
+    <row r="756">
+      <c r="A756" s="2" t="inlineStr">
+        <is>
+          <t>FS749</t>
+        </is>
+      </c>
+      <c r="B756" s="2" t="inlineStr">
+        <is>
+          <t>510492000001572004</t>
+        </is>
+      </c>
+      <c r="C756" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D756" s="2" t="inlineStr">
+        <is>
+          <t>510492000001517001</t>
+        </is>
+      </c>
+      <c r="E756" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F756" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G756" s="2" t="inlineStr">
+        <is>
+          <t>120.000</t>
+        </is>
+      </c>
+      <c r="H756" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I756" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J756" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K756" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L756" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M756" s="2" t="inlineStr">
+        <is>
+          <t>749</t>
+        </is>
+      </c>
+      <c r="N756" s="2" t="inlineStr">
+        <is>
+          <t>Max Out Tutoring</t>
+        </is>
+      </c>
+      <c r="O756" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P756" s="5" t="n">
+        <v>46293.0</v>
+      </c>
+      <c r="Q756" s="6" t="n">
+        <v>46296.39642361111</v>
+      </c>
+      <c r="R756" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S756" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T756" s="2" t="inlineStr">
+        <is>
+          <t>510492000001572008</t>
+        </is>
+      </c>
+      <c r="U756" s="2" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="V756" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W756" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X756" s="2" t="inlineStr">
+        <is>
+          <t>242120</t>
+        </is>
+      </c>
+      <c r="Y756" s="5" t="n">
+        <v>46277.0</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="2" t="inlineStr">
+        <is>
+          <t>FS750</t>
+        </is>
+      </c>
+      <c r="B757" s="2" t="inlineStr">
+        <is>
+          <t>510492000001572022</t>
+        </is>
+      </c>
+      <c r="C757" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D757" s="2" t="inlineStr">
+        <is>
+          <t>510492000001517001</t>
+        </is>
+      </c>
+      <c r="E757" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F757" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G757" s="2" t="inlineStr">
+        <is>
+          <t>120.000</t>
+        </is>
+      </c>
+      <c r="H757" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I757" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J757" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K757" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L757" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M757" s="2" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="N757" s="2" t="inlineStr">
+        <is>
+          <t>Max Out Tutoring</t>
+        </is>
+      </c>
+      <c r="O757" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P757" s="5" t="n">
+        <v>46293.0</v>
+      </c>
+      <c r="Q757" s="6" t="n">
+        <v>46296.39677083334</v>
+      </c>
+      <c r="R757" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S757" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T757" s="2" t="inlineStr">
+        <is>
+          <t>510492000001572026</t>
+        </is>
+      </c>
+      <c r="U757" s="2" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="V757" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W757" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X757" s="2" t="inlineStr">
+        <is>
+          <t>242121</t>
+        </is>
+      </c>
+      <c r="Y757" s="5" t="n">
+        <v>46279.0</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="2" t="inlineStr">
+        <is>
+          <t>FS751</t>
+        </is>
+      </c>
+      <c r="B758" s="2" t="inlineStr">
+        <is>
+          <t>510492000001572040</t>
+        </is>
+      </c>
+      <c r="C758" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D758" s="2" t="inlineStr">
+        <is>
+          <t>510492000001436106</t>
+        </is>
+      </c>
+      <c r="E758" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F758" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G758" s="2" t="inlineStr">
+        <is>
+          <t>100.000</t>
+        </is>
+      </c>
+      <c r="H758" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I758" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J758" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K758" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L758" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M758" s="2" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
+      <c r="N758" s="2" t="inlineStr">
+        <is>
+          <t>RICHMOND TOTO PROFESSIONAL CLEANING LTD</t>
+        </is>
+      </c>
+      <c r="O758" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P758" s="5" t="n">
+        <v>46293.0</v>
+      </c>
+      <c r="Q758" s="6" t="n">
+        <v>46296.39711805555</v>
+      </c>
+      <c r="R758" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S758" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T758" s="2" t="inlineStr">
+        <is>
+          <t>510492000001572044</t>
+        </is>
+      </c>
+      <c r="U758" s="2" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="V758" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W758" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X758" s="2" t="inlineStr">
+        <is>
+          <t>242134</t>
+        </is>
+      </c>
+      <c r="Y758" s="5" t="n">
+        <v>46290.0</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="2" t="inlineStr">
+        <is>
+          <t>FS752</t>
+        </is>
+      </c>
+      <c r="B759" s="2" t="inlineStr">
+        <is>
+          <t>510492000001572058</t>
+        </is>
+      </c>
+      <c r="C759" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D759" s="2" t="inlineStr">
+        <is>
+          <t>510492000001551001</t>
+        </is>
+      </c>
+      <c r="E759" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F759" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G759" s="2" t="inlineStr">
+        <is>
+          <t>180.000</t>
+        </is>
+      </c>
+      <c r="H759" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I759" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J759" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K759" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L759" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M759" s="2" t="inlineStr">
+        <is>
+          <t>752</t>
+        </is>
+      </c>
+      <c r="N759" s="2" t="inlineStr">
+        <is>
+          <t>PARTY SUPPLYS LTD</t>
+        </is>
+      </c>
+      <c r="O759" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P759" s="5" t="n">
+        <v>46293.0</v>
+      </c>
+      <c r="Q759" s="6" t="n">
+        <v>46296.39739583333</v>
+      </c>
+      <c r="R759" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S759" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T759" s="2" t="inlineStr">
+        <is>
+          <t>510492000001572062</t>
+        </is>
+      </c>
+      <c r="U759" s="2" t="n">
+        <v>180.0</v>
+      </c>
+      <c r="V759" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W759" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X759" s="2" t="inlineStr">
+        <is>
+          <t>242135</t>
+        </is>
+      </c>
+      <c r="Y759" s="5" t="n">
+        <v>46291.0</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="2" t="inlineStr">
+        <is>
+          <t>FS753</t>
+        </is>
+      </c>
+      <c r="B760" s="2" t="inlineStr">
+        <is>
+          <t>510492000001572076</t>
+        </is>
+      </c>
+      <c r="C760" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D760" s="2" t="inlineStr">
+        <is>
+          <t>510492000001450146</t>
+        </is>
+      </c>
+      <c r="E760" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F760" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G760" s="2" t="inlineStr">
+        <is>
+          <t>120.000</t>
+        </is>
+      </c>
+      <c r="H760" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I760" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J760" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K760" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L760" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M760" s="2" t="inlineStr">
+        <is>
+          <t>753</t>
+        </is>
+      </c>
+      <c r="N760" s="2" t="inlineStr">
+        <is>
+          <t>Mr. Phone Mobile &amp; Vape</t>
+        </is>
+      </c>
+      <c r="O760" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P760" s="5" t="n">
+        <v>46294.0</v>
+      </c>
+      <c r="Q760" s="6" t="n">
+        <v>46296.39769675926</v>
+      </c>
+      <c r="R760" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S760" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T760" s="2" t="inlineStr">
+        <is>
+          <t>510492000001572080</t>
+        </is>
+      </c>
+      <c r="U760" s="2" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="V760" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W760" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X760" s="2" t="inlineStr">
+        <is>
+          <t>242131</t>
+        </is>
+      </c>
+      <c r="Y760" s="5" t="n">
+        <v>46286.0</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="2" t="inlineStr">
+        <is>
+          <t>FS754</t>
+        </is>
+      </c>
+      <c r="B761" s="2" t="inlineStr">
+        <is>
+          <t>510492000001572094</t>
+        </is>
+      </c>
+      <c r="C761" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D761" s="2" t="inlineStr">
+        <is>
+          <t>510492000000560319</t>
+        </is>
+      </c>
+      <c r="E761" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F761" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G761" s="2" t="inlineStr">
+        <is>
+          <t>240.000</t>
+        </is>
+      </c>
+      <c r="H761" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I761" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J761" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K761" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L761" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M761" s="2" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="N761" s="2" t="inlineStr">
+        <is>
+          <t>RRJ Carpentry and Joinery Ltd</t>
+        </is>
+      </c>
+      <c r="O761" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P761" s="5" t="n">
+        <v>46295.0</v>
+      </c>
+      <c r="Q761" s="6" t="n">
+        <v>46296.39803240741</v>
+      </c>
+      <c r="R761" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S761" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T761" s="2" t="inlineStr">
+        <is>
+          <t>510492000001572098</t>
+        </is>
+      </c>
+      <c r="U761" s="2" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="V761" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W761" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X761" s="2" t="inlineStr">
+        <is>
+          <t>241925</t>
+        </is>
+      </c>
+      <c r="Y761" s="5" t="n">
+        <v>46143.0</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="2" t="inlineStr">
+        <is>
+          <t>FS755</t>
+        </is>
+      </c>
+      <c r="B762" s="2" t="inlineStr">
+        <is>
+          <t>510492000001572112</t>
+        </is>
+      </c>
+      <c r="C762" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D762" s="2" t="inlineStr">
+        <is>
+          <t>510492000000560319</t>
+        </is>
+      </c>
+      <c r="E762" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F762" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G762" s="2" t="inlineStr">
+        <is>
+          <t>10.000</t>
+        </is>
+      </c>
+      <c r="H762" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I762" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J762" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K762" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L762" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M762" s="2" t="inlineStr">
+        <is>
+          <t>755</t>
+        </is>
+      </c>
+      <c r="N762" s="2" t="inlineStr">
+        <is>
+          <t>RRJ Carpentry and Joinery Ltd</t>
+        </is>
+      </c>
+      <c r="O762" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P762" s="5" t="n">
+        <v>46295.0</v>
+      </c>
+      <c r="Q762" s="6" t="n">
+        <v>46296.39822916667</v>
+      </c>
+      <c r="R762" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S762" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T762" s="2" t="inlineStr">
+        <is>
+          <t>510492000001572116</t>
+        </is>
+      </c>
+      <c r="U762" s="2" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="V762" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W762" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X762" s="2" t="inlineStr">
+        <is>
+          <t>241962</t>
+        </is>
+      </c>
+      <c r="Y762" s="5" t="n">
+        <v>46174.0</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="2" t="inlineStr">
+        <is>
+          <t>FS756</t>
+        </is>
+      </c>
+      <c r="B763" s="2" t="inlineStr">
+        <is>
+          <t>510492000001573105</t>
+        </is>
+      </c>
+      <c r="C763" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D763" s="2" t="inlineStr">
+        <is>
+          <t>510492000000327139</t>
+        </is>
+      </c>
+      <c r="E763" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F763" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G763" s="2" t="inlineStr">
+        <is>
+          <t>400.000</t>
+        </is>
+      </c>
+      <c r="H763" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I763" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J763" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K763" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L763" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M763" s="2" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="N763" s="2" t="inlineStr">
+        <is>
+          <t>BATHROOMS LONDON LIMITED</t>
+        </is>
+      </c>
+      <c r="O763" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P763" s="5" t="n">
+        <v>46296.0</v>
+      </c>
+      <c r="Q763" s="6" t="n">
+        <v>46297.59375</v>
+      </c>
+      <c r="R763" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S763" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T763" s="2" t="inlineStr">
+        <is>
+          <t>510492000001573109</t>
+        </is>
+      </c>
+      <c r="U763" s="2" t="n">
+        <v>400.0</v>
+      </c>
+      <c r="V763" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W763" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X763" s="2" t="inlineStr">
+        <is>
+          <t>242132</t>
+        </is>
+      </c>
+      <c r="Y763" s="5" t="n">
+        <v>46288.0</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="2" t="inlineStr">
+        <is>
+          <t>FS757</t>
+        </is>
+      </c>
+      <c r="B764" s="2" t="inlineStr">
+        <is>
+          <t>510492000001573123</t>
+        </is>
+      </c>
+      <c r="C764" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D764" s="2" t="inlineStr">
+        <is>
+          <t>510492000000541229</t>
+        </is>
+      </c>
+      <c r="E764" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F764" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G764" s="2" t="inlineStr">
+        <is>
+          <t>100.000</t>
+        </is>
+      </c>
+      <c r="H764" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I764" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J764" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K764" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L764" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M764" s="2" t="inlineStr">
+        <is>
+          <t>757</t>
+        </is>
+      </c>
+      <c r="N764" s="2" t="inlineStr">
+        <is>
+          <t>Optimum Global Care</t>
+        </is>
+      </c>
+      <c r="O764" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P764" s="5" t="n">
+        <v>46296.0</v>
+      </c>
+      <c r="Q764" s="6" t="n">
+        <v>46297.59405092592</v>
+      </c>
+      <c r="R764" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S764" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T764" s="2" t="inlineStr">
+        <is>
+          <t>510492000001573127</t>
+        </is>
+      </c>
+      <c r="U764" s="2" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="V764" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W764" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X764" s="2" t="inlineStr">
+        <is>
+          <t>242164</t>
+        </is>
+      </c>
+      <c r="Y764" s="5" t="n">
+        <v>46296.0</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="2" t="inlineStr">
+        <is>
+          <t>FS758</t>
+        </is>
+      </c>
+      <c r="B765" s="2" t="inlineStr">
+        <is>
+          <t>510492000001573141</t>
+        </is>
+      </c>
+      <c r="C765" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D765" s="2" t="inlineStr">
+        <is>
+          <t>510492000000560319</t>
+        </is>
+      </c>
+      <c r="E765" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F765" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G765" s="2" t="inlineStr">
+        <is>
+          <t>250.000</t>
+        </is>
+      </c>
+      <c r="H765" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I765" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J765" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K765" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L765" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M765" s="2" t="inlineStr">
+        <is>
+          <t>758</t>
+        </is>
+      </c>
+      <c r="N765" s="2" t="inlineStr">
+        <is>
+          <t>RRJ Carpentry and Joinery Ltd</t>
+        </is>
+      </c>
+      <c r="O765" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P765" s="5" t="n">
+        <v>46297.0</v>
+      </c>
+      <c r="Q765" s="6" t="n">
+        <v>46297.59460648148</v>
+      </c>
+      <c r="R765" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S765" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T765" s="2" t="inlineStr">
+        <is>
+          <t>510492000001573145</t>
+        </is>
+      </c>
+      <c r="U765" s="2" t="n">
+        <v>250.0</v>
+      </c>
+      <c r="V765" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W765" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X765" s="2" t="inlineStr">
+        <is>
+          <t>242167</t>
+        </is>
+      </c>
+      <c r="Y765" s="5" t="n">
+        <v>46297.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Customer_Payment_zoho.xlsx
+++ b/Customer_Payment_zoho.xlsx
@@ -86,7 +86,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y765"/>
+  <dimension ref="A1:Y769"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.53125" customWidth="true"/>
@@ -89733,6 +89733,474 @@
         <v>46297.0</v>
       </c>
     </row>
+    <row r="766">
+      <c r="A766" s="2" t="inlineStr">
+        <is>
+          <t>FS759</t>
+        </is>
+      </c>
+      <c r="B766" s="2" t="inlineStr">
+        <is>
+          <t>510492000001582020</t>
+        </is>
+      </c>
+      <c r="C766" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D766" s="2" t="inlineStr">
+        <is>
+          <t>510492000001324001</t>
+        </is>
+      </c>
+      <c r="E766" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F766" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G766" s="2" t="inlineStr">
+        <is>
+          <t>1000.000</t>
+        </is>
+      </c>
+      <c r="H766" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I766" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J766" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K766" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L766" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M766" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="N766" s="2" t="inlineStr">
+        <is>
+          <t>READING PROPERTIES GROUP LTD</t>
+        </is>
+      </c>
+      <c r="O766" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P766" s="5" t="n">
+        <v>46296.0</v>
+      </c>
+      <c r="Q766" s="6" t="n">
+        <v>46301.57712962963</v>
+      </c>
+      <c r="R766" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S766" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T766" s="2" t="inlineStr">
+        <is>
+          <t>510492000001582024</t>
+        </is>
+      </c>
+      <c r="U766" s="2" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="V766" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W766" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X766" s="2" t="inlineStr">
+        <is>
+          <t>242116</t>
+        </is>
+      </c>
+      <c r="Y766" s="5" t="n">
+        <v>46296.0</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="2" t="inlineStr">
+        <is>
+          <t>FS760</t>
+        </is>
+      </c>
+      <c r="B767" s="2" t="inlineStr">
+        <is>
+          <t>510492000001582099</t>
+        </is>
+      </c>
+      <c r="C767" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D767" s="2" t="inlineStr">
+        <is>
+          <t>510492000000122647</t>
+        </is>
+      </c>
+      <c r="E767" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F767" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G767" s="2" t="inlineStr">
+        <is>
+          <t>718.800</t>
+        </is>
+      </c>
+      <c r="H767" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I767" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J767" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K767" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L767" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M767" s="2" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="N767" s="2" t="inlineStr">
+        <is>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+        </is>
+      </c>
+      <c r="O767" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P767" s="5" t="n">
+        <v>46300.0</v>
+      </c>
+      <c r="Q767" s="6" t="n">
+        <v>46302.49916666667</v>
+      </c>
+      <c r="R767" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S767" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T767" s="2" t="inlineStr">
+        <is>
+          <t>510492000001582103</t>
+        </is>
+      </c>
+      <c r="U767" s="2" t="n">
+        <v>718.8</v>
+      </c>
+      <c r="V767" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W767" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X767" s="2" t="inlineStr">
+        <is>
+          <t>242068</t>
+        </is>
+      </c>
+      <c r="Y767" s="5" t="n">
+        <v>46248.0</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="2" t="inlineStr">
+        <is>
+          <t>FS761</t>
+        </is>
+      </c>
+      <c r="B768" s="2" t="inlineStr">
+        <is>
+          <t>510492000001582118</t>
+        </is>
+      </c>
+      <c r="C768" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D768" s="2" t="inlineStr">
+        <is>
+          <t>510492000000122647</t>
+        </is>
+      </c>
+      <c r="E768" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F768" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G768" s="2" t="inlineStr">
+        <is>
+          <t>238.800</t>
+        </is>
+      </c>
+      <c r="H768" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I768" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J768" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K768" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L768" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M768" s="2" t="inlineStr">
+        <is>
+          <t>761</t>
+        </is>
+      </c>
+      <c r="N768" s="2" t="inlineStr">
+        <is>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+        </is>
+      </c>
+      <c r="O768" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P768" s="5" t="n">
+        <v>46300.0</v>
+      </c>
+      <c r="Q768" s="6" t="n">
+        <v>46302.49936342592</v>
+      </c>
+      <c r="R768" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S768" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T768" s="2" t="inlineStr">
+        <is>
+          <t>510492000001582122</t>
+        </is>
+      </c>
+      <c r="U768" s="2" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="V768" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W768" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X768" s="2" t="inlineStr">
+        <is>
+          <t>242032</t>
+        </is>
+      </c>
+      <c r="Y768" s="5" t="n">
+        <v>46235.0</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="2" t="inlineStr">
+        <is>
+          <t>FS762</t>
+        </is>
+      </c>
+      <c r="B769" s="2" t="inlineStr">
+        <is>
+          <t>510492000001582137</t>
+        </is>
+      </c>
+      <c r="C769" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D769" s="2" t="inlineStr">
+        <is>
+          <t>510492000001155001</t>
+        </is>
+      </c>
+      <c r="E769" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F769" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G769" s="2" t="inlineStr">
+        <is>
+          <t>360.000</t>
+        </is>
+      </c>
+      <c r="H769" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I769" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J769" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K769" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L769" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M769" s="2" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="N769" s="2" t="inlineStr">
+        <is>
+          <t>Galloway Pest Control</t>
+        </is>
+      </c>
+      <c r="O769" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P769" s="5" t="n">
+        <v>46300.0</v>
+      </c>
+      <c r="Q769" s="6" t="n">
+        <v>46302.49962962963</v>
+      </c>
+      <c r="R769" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S769" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T769" s="2" t="inlineStr">
+        <is>
+          <t>510492000001582141</t>
+        </is>
+      </c>
+      <c r="U769" s="2" t="n">
+        <v>360.0</v>
+      </c>
+      <c r="V769" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W769" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X769" s="2" t="inlineStr">
+        <is>
+          <t>242165</t>
+        </is>
+      </c>
+      <c r="Y769" s="5" t="n">
+        <v>46296.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Customer_Payment_zoho.xlsx
+++ b/Customer_Payment_zoho.xlsx
@@ -86,7 +86,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y769"/>
+  <dimension ref="A1:Y773"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.53125" customWidth="true"/>
@@ -90201,6 +90201,474 @@
         <v>46296.0</v>
       </c>
     </row>
+    <row r="770">
+      <c r="A770" s="2" t="inlineStr">
+        <is>
+          <t>FS763</t>
+        </is>
+      </c>
+      <c r="B770" s="2" t="inlineStr">
+        <is>
+          <t>510492000001587002</t>
+        </is>
+      </c>
+      <c r="C770" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D770" s="2" t="inlineStr">
+        <is>
+          <t>510492000001582038</t>
+        </is>
+      </c>
+      <c r="E770" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F770" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G770" s="2" t="inlineStr">
+        <is>
+          <t>250.000</t>
+        </is>
+      </c>
+      <c r="H770" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I770" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J770" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K770" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L770" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M770" s="2" t="inlineStr">
+        <is>
+          <t>763</t>
+        </is>
+      </c>
+      <c r="N770" s="2" t="inlineStr">
+        <is>
+          <t>CONNECT DRIVING SCHOOL LIMITED</t>
+        </is>
+      </c>
+      <c r="O770" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P770" s="5" t="n">
+        <v>46302.0</v>
+      </c>
+      <c r="Q770" s="6" t="n">
+        <v>46303.59953703704</v>
+      </c>
+      <c r="R770" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S770" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T770" s="2" t="inlineStr">
+        <is>
+          <t>510492000001587006</t>
+        </is>
+      </c>
+      <c r="U770" s="2" t="n">
+        <v>250.0</v>
+      </c>
+      <c r="V770" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W770" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X770" s="2" t="inlineStr">
+        <is>
+          <t>242168</t>
+        </is>
+      </c>
+      <c r="Y770" s="5" t="n">
+        <v>46301.0</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="2" t="inlineStr">
+        <is>
+          <t>FS764</t>
+        </is>
+      </c>
+      <c r="B771" s="2" t="inlineStr">
+        <is>
+          <t>510492000001587021</t>
+        </is>
+      </c>
+      <c r="C771" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D771" s="2" t="inlineStr">
+        <is>
+          <t>510492000001582067</t>
+        </is>
+      </c>
+      <c r="E771" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F771" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G771" s="2" t="inlineStr">
+        <is>
+          <t>100.000</t>
+        </is>
+      </c>
+      <c r="H771" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I771" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J771" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K771" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L771" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M771" s="2" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="N771" s="2" t="inlineStr">
+        <is>
+          <t>BOILER GAS TECH LIMITED</t>
+        </is>
+      </c>
+      <c r="O771" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P771" s="5" t="n">
+        <v>46302.0</v>
+      </c>
+      <c r="Q771" s="6" t="n">
+        <v>46303.60020833334</v>
+      </c>
+      <c r="R771" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S771" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T771" s="2" t="inlineStr">
+        <is>
+          <t>510492000001587025</t>
+        </is>
+      </c>
+      <c r="U771" s="2" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="V771" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W771" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X771" s="2" t="inlineStr">
+        <is>
+          <t>242169</t>
+        </is>
+      </c>
+      <c r="Y771" s="5" t="n">
+        <v>46302.0</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="2" t="inlineStr">
+        <is>
+          <t>FS765</t>
+        </is>
+      </c>
+      <c r="B772" s="2" t="inlineStr">
+        <is>
+          <t>510492000001587040</t>
+        </is>
+      </c>
+      <c r="C772" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D772" s="2" t="inlineStr">
+        <is>
+          <t>510492000000505059</t>
+        </is>
+      </c>
+      <c r="E772" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F772" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G772" s="2" t="inlineStr">
+        <is>
+          <t>120.000</t>
+        </is>
+      </c>
+      <c r="H772" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I772" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J772" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K772" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L772" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M772" s="2" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="N772" s="2" t="inlineStr">
+        <is>
+          <t>Chorus Music Therapy &amp; Education</t>
+        </is>
+      </c>
+      <c r="O772" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P772" s="5" t="n">
+        <v>46302.0</v>
+      </c>
+      <c r="Q772" s="6" t="n">
+        <v>46303.60053240741</v>
+      </c>
+      <c r="R772" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S772" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T772" s="2" t="inlineStr">
+        <is>
+          <t>510492000001587044</t>
+        </is>
+      </c>
+      <c r="U772" s="2" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="V772" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W772" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X772" s="2" t="inlineStr">
+        <is>
+          <t>242095</t>
+        </is>
+      </c>
+      <c r="Y772" s="5" t="n">
+        <v>46266.0</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="2" t="inlineStr">
+        <is>
+          <t>FS766</t>
+        </is>
+      </c>
+      <c r="B773" s="2" t="inlineStr">
+        <is>
+          <t>510492000001587059</t>
+        </is>
+      </c>
+      <c r="C773" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D773" s="2" t="inlineStr">
+        <is>
+          <t>510492000000742001</t>
+        </is>
+      </c>
+      <c r="E773" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F773" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G773" s="2" t="inlineStr">
+        <is>
+          <t>240.000</t>
+        </is>
+      </c>
+      <c r="H773" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I773" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J773" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K773" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L773" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M773" s="2" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="N773" s="2" t="inlineStr">
+        <is>
+          <t>Adam’s Painting and Decorating</t>
+        </is>
+      </c>
+      <c r="O773" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P773" s="5" t="n">
+        <v>46302.0</v>
+      </c>
+      <c r="Q773" s="6" t="n">
+        <v>46303.60082175926</v>
+      </c>
+      <c r="R773" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S773" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T773" s="2" t="inlineStr">
+        <is>
+          <t>510492000001587063</t>
+        </is>
+      </c>
+      <c r="U773" s="2" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="V773" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W773" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X773" s="2" t="inlineStr">
+        <is>
+          <t>242152</t>
+        </is>
+      </c>
+      <c r="Y773" s="5" t="n">
+        <v>46296.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Customer_Payment_zoho.xlsx
+++ b/Customer_Payment_zoho.xlsx
@@ -86,7 +86,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y773"/>
+  <dimension ref="A1:Y777"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.53125" customWidth="true"/>
@@ -90669,6 +90669,474 @@
         <v>46296.0</v>
       </c>
     </row>
+    <row r="774">
+      <c r="A774" s="2" t="inlineStr">
+        <is>
+          <t>FS767</t>
+        </is>
+      </c>
+      <c r="B774" s="2" t="inlineStr">
+        <is>
+          <t>510492000001594002</t>
+        </is>
+      </c>
+      <c r="C774" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D774" s="2" t="inlineStr">
+        <is>
+          <t>510492000000123277</t>
+        </is>
+      </c>
+      <c r="E774" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F774" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G774" s="2" t="inlineStr">
+        <is>
+          <t>238.800</t>
+        </is>
+      </c>
+      <c r="H774" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I774" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J774" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K774" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L774" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M774" s="2" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="N774" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Shoes Limited</t>
+        </is>
+      </c>
+      <c r="O774" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P774" s="5" t="n">
+        <v>46304.0</v>
+      </c>
+      <c r="Q774" s="6" t="n">
+        <v>46305.71412037037</v>
+      </c>
+      <c r="R774" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S774" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T774" s="2" t="inlineStr">
+        <is>
+          <t>510492000001594006</t>
+        </is>
+      </c>
+      <c r="U774" s="2" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="V774" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W774" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X774" s="2" t="inlineStr">
+        <is>
+          <t>241987</t>
+        </is>
+      </c>
+      <c r="Y774" s="5" t="n">
+        <v>46204.0</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="2" t="inlineStr">
+        <is>
+          <t>FS768</t>
+        </is>
+      </c>
+      <c r="B775" s="2" t="inlineStr">
+        <is>
+          <t>510492000001594021</t>
+        </is>
+      </c>
+      <c r="C775" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D775" s="2" t="inlineStr">
+        <is>
+          <t>510492000000123277</t>
+        </is>
+      </c>
+      <c r="E775" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F775" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G775" s="2" t="inlineStr">
+        <is>
+          <t>240.000</t>
+        </is>
+      </c>
+      <c r="H775" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I775" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J775" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K775" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L775" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M775" s="2" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="N775" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Shoes Limited</t>
+        </is>
+      </c>
+      <c r="O775" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P775" s="5" t="n">
+        <v>46304.0</v>
+      </c>
+      <c r="Q775" s="6" t="n">
+        <v>46305.71431712963</v>
+      </c>
+      <c r="R775" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S775" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T775" s="2" t="inlineStr">
+        <is>
+          <t>510492000001594025</t>
+        </is>
+      </c>
+      <c r="U775" s="2" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="V775" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W775" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X775" s="2" t="inlineStr">
+        <is>
+          <t>242005</t>
+        </is>
+      </c>
+      <c r="Y775" s="5" t="n">
+        <v>46204.0</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="2" t="inlineStr">
+        <is>
+          <t>FS769</t>
+        </is>
+      </c>
+      <c r="B776" s="2" t="inlineStr">
+        <is>
+          <t>510492000001594040</t>
+        </is>
+      </c>
+      <c r="C776" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D776" s="2" t="inlineStr">
+        <is>
+          <t>510492000000123277</t>
+        </is>
+      </c>
+      <c r="E776" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F776" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G776" s="2" t="inlineStr">
+        <is>
+          <t>238.800</t>
+        </is>
+      </c>
+      <c r="H776" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I776" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J776" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K776" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L776" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M776" s="2" t="inlineStr">
+        <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="N776" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Shoes Limited</t>
+        </is>
+      </c>
+      <c r="O776" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P776" s="5" t="n">
+        <v>46304.0</v>
+      </c>
+      <c r="Q776" s="6" t="n">
+        <v>46305.71467592593</v>
+      </c>
+      <c r="R776" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S776" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T776" s="2" t="inlineStr">
+        <is>
+          <t>510492000001594044</t>
+        </is>
+      </c>
+      <c r="U776" s="2" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="V776" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W776" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X776" s="2" t="inlineStr">
+        <is>
+          <t>242035</t>
+        </is>
+      </c>
+      <c r="Y776" s="5" t="n">
+        <v>46235.0</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="2" t="inlineStr">
+        <is>
+          <t>FS770</t>
+        </is>
+      </c>
+      <c r="B777" s="2" t="inlineStr">
+        <is>
+          <t>510492000001600004</t>
+        </is>
+      </c>
+      <c r="C777" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D777" s="2" t="inlineStr">
+        <is>
+          <t>510492000001561001</t>
+        </is>
+      </c>
+      <c r="E777" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F777" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G777" s="2" t="inlineStr">
+        <is>
+          <t>300.000</t>
+        </is>
+      </c>
+      <c r="H777" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I777" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J777" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K777" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L777" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M777" s="2" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="N777" s="2" t="inlineStr">
+        <is>
+          <t>BURTON DRIVING SCHOOL LTD</t>
+        </is>
+      </c>
+      <c r="O777" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P777" s="5" t="n">
+        <v>46302.0</v>
+      </c>
+      <c r="Q777" s="6" t="n">
+        <v>46307.52086805556</v>
+      </c>
+      <c r="R777" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S777" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T777" s="2" t="inlineStr">
+        <is>
+          <t>510492000001600008</t>
+        </is>
+      </c>
+      <c r="U777" s="2" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="V777" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W777" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X777" s="2" t="inlineStr">
+        <is>
+          <t>242136</t>
+        </is>
+      </c>
+      <c r="Y777" s="5" t="n">
+        <v>46294.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Customer_Payment_zoho.xlsx
+++ b/Customer_Payment_zoho.xlsx
@@ -86,7 +86,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y777"/>
+  <dimension ref="A1:Y786"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.53125" customWidth="true"/>
@@ -91137,6 +91137,1059 @@
         <v>46294.0</v>
       </c>
     </row>
+    <row r="778">
+      <c r="A778" s="2" t="inlineStr">
+        <is>
+          <t>FS771</t>
+        </is>
+      </c>
+      <c r="B778" s="2" t="inlineStr">
+        <is>
+          <t>510492000001614044</t>
+        </is>
+      </c>
+      <c r="C778" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D778" s="2" t="inlineStr">
+        <is>
+          <t>510492000001564001</t>
+        </is>
+      </c>
+      <c r="E778" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F778" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G778" s="2" t="inlineStr">
+        <is>
+          <t>642.530</t>
+        </is>
+      </c>
+      <c r="H778" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I778" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J778" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K778" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L778" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M778" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="N778" s="2" t="inlineStr">
+        <is>
+          <t>Stabilus Safety GmbH</t>
+        </is>
+      </c>
+      <c r="O778" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P778" s="5" t="n">
+        <v>46317.0</v>
+      </c>
+      <c r="Q778" s="6" t="n">
+        <v>46317.74732638889</v>
+      </c>
+      <c r="R778" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S778" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T778" s="2" t="inlineStr">
+        <is>
+          <t>510492000001614048</t>
+        </is>
+      </c>
+      <c r="U778" s="2" t="n">
+        <v>642.53</v>
+      </c>
+      <c r="V778" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W778" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X778" s="2" t="inlineStr">
+        <is>
+          <t>242137</t>
+        </is>
+      </c>
+      <c r="Y778" s="5" t="n">
+        <v>46294.0</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="2" t="inlineStr">
+        <is>
+          <t>FS772</t>
+        </is>
+      </c>
+      <c r="B779" s="2" t="inlineStr">
+        <is>
+          <t>510492000001614063</t>
+        </is>
+      </c>
+      <c r="C779" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D779" s="2" t="inlineStr">
+        <is>
+          <t>510492000001582038</t>
+        </is>
+      </c>
+      <c r="E779" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F779" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G779" s="2" t="inlineStr">
+        <is>
+          <t>370.000</t>
+        </is>
+      </c>
+      <c r="H779" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I779" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J779" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K779" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L779" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M779" s="2" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="N779" s="2" t="inlineStr">
+        <is>
+          <t>CONNECT DRIVING SCHOOL LIMITED</t>
+        </is>
+      </c>
+      <c r="O779" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P779" s="5" t="n">
+        <v>46310.0</v>
+      </c>
+      <c r="Q779" s="6" t="n">
+        <v>46317.74821759259</v>
+      </c>
+      <c r="R779" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S779" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T779" s="2" t="inlineStr">
+        <is>
+          <t>510492000001614067</t>
+        </is>
+      </c>
+      <c r="U779" s="2" t="n">
+        <v>370.0</v>
+      </c>
+      <c r="V779" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W779" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X779" s="2" t="inlineStr">
+        <is>
+          <t>242168</t>
+        </is>
+      </c>
+      <c r="Y779" s="5" t="n">
+        <v>46301.0</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="2" t="inlineStr">
+        <is>
+          <t>FS773</t>
+        </is>
+      </c>
+      <c r="B780" s="2" t="inlineStr">
+        <is>
+          <t>510492000001614082</t>
+        </is>
+      </c>
+      <c r="C780" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D780" s="2" t="inlineStr">
+        <is>
+          <t>510492000001025001</t>
+        </is>
+      </c>
+      <c r="E780" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F780" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G780" s="2" t="inlineStr">
+        <is>
+          <t>125.000</t>
+        </is>
+      </c>
+      <c r="H780" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I780" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J780" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K780" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L780" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M780" s="2" t="inlineStr">
+        <is>
+          <t>773</t>
+        </is>
+      </c>
+      <c r="N780" s="2" t="inlineStr">
+        <is>
+          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
+        </is>
+      </c>
+      <c r="O780" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P780" s="5" t="n">
+        <v>46310.0</v>
+      </c>
+      <c r="Q780" s="6" t="n">
+        <v>46317.748564814814</v>
+      </c>
+      <c r="R780" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S780" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T780" s="2" t="inlineStr">
+        <is>
+          <t>510492000001614086</t>
+        </is>
+      </c>
+      <c r="U780" s="2" t="n">
+        <v>125.0</v>
+      </c>
+      <c r="V780" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W780" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X780" s="2" t="inlineStr">
+        <is>
+          <t>242127</t>
+        </is>
+      </c>
+      <c r="Y780" s="5" t="n">
+        <v>46280.0</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="2" t="inlineStr">
+        <is>
+          <t>FS774</t>
+        </is>
+      </c>
+      <c r="B781" s="2" t="inlineStr">
+        <is>
+          <t>510492000001631002</t>
+        </is>
+      </c>
+      <c r="C781" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D781" s="2" t="inlineStr">
+        <is>
+          <t>510492000001628039</t>
+        </is>
+      </c>
+      <c r="E781" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F781" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G781" s="2" t="inlineStr">
+        <is>
+          <t>600.000</t>
+        </is>
+      </c>
+      <c r="H781" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I781" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J781" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K781" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L781" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M781" s="2" t="inlineStr">
+        <is>
+          <t>774</t>
+        </is>
+      </c>
+      <c r="N781" s="2" t="inlineStr">
+        <is>
+          <t>TAILORED TOURS LTD</t>
+        </is>
+      </c>
+      <c r="O781" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P781" s="5" t="n">
+        <v>46322.0</v>
+      </c>
+      <c r="Q781" s="6" t="n">
+        <v>46323.627384259256</v>
+      </c>
+      <c r="R781" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S781" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T781" s="2" t="inlineStr">
+        <is>
+          <t>510492000001631006</t>
+        </is>
+      </c>
+      <c r="U781" s="2" t="n">
+        <v>600.0</v>
+      </c>
+      <c r="V781" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W781" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X781" s="2" t="inlineStr">
+        <is>
+          <t>242178</t>
+        </is>
+      </c>
+      <c r="Y781" s="5" t="n">
+        <v>46322.0</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="2" t="inlineStr">
+        <is>
+          <t>FS775</t>
+        </is>
+      </c>
+      <c r="B782" s="2" t="inlineStr">
+        <is>
+          <t>510492000001631021</t>
+        </is>
+      </c>
+      <c r="C782" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D782" s="2" t="inlineStr">
+        <is>
+          <t>510492000001614001</t>
+        </is>
+      </c>
+      <c r="E782" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F782" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G782" s="2" t="inlineStr">
+        <is>
+          <t>200.000</t>
+        </is>
+      </c>
+      <c r="H782" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I782" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J782" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K782" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L782" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M782" s="2" t="inlineStr">
+        <is>
+          <t>775</t>
+        </is>
+      </c>
+      <c r="N782" s="2" t="inlineStr">
+        <is>
+          <t>Kumon Huntingdon</t>
+        </is>
+      </c>
+      <c r="O782" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P782" s="5" t="n">
+        <v>46318.0</v>
+      </c>
+      <c r="Q782" s="6" t="n">
+        <v>46323.62829861111</v>
+      </c>
+      <c r="R782" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S782" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T782" s="2" t="inlineStr">
+        <is>
+          <t>510492000001631025</t>
+        </is>
+      </c>
+      <c r="U782" s="2" t="n">
+        <v>200.0</v>
+      </c>
+      <c r="V782" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W782" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X782" s="2" t="inlineStr">
+        <is>
+          <t>242174</t>
+        </is>
+      </c>
+      <c r="Y782" s="5" t="n">
+        <v>46317.0</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="2" t="inlineStr">
+        <is>
+          <t>FS776</t>
+        </is>
+      </c>
+      <c r="B783" s="2" t="inlineStr">
+        <is>
+          <t>510492000001631040</t>
+        </is>
+      </c>
+      <c r="C783" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D783" s="2" t="inlineStr">
+        <is>
+          <t>510492000001628001</t>
+        </is>
+      </c>
+      <c r="E783" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F783" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G783" s="2" t="inlineStr">
+        <is>
+          <t>115.000</t>
+        </is>
+      </c>
+      <c r="H783" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I783" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J783" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K783" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L783" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M783" s="2" t="inlineStr">
+        <is>
+          <t>776</t>
+        </is>
+      </c>
+      <c r="N783" s="2" t="inlineStr">
+        <is>
+          <t>QMFOOTPRINT TINEY HOME NURSERY LTD</t>
+        </is>
+      </c>
+      <c r="O783" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P783" s="5" t="n">
+        <v>46322.0</v>
+      </c>
+      <c r="Q783" s="6" t="n">
+        <v>46323.630057870374</v>
+      </c>
+      <c r="R783" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S783" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T783" s="2" t="inlineStr">
+        <is>
+          <t>510492000001631044</t>
+        </is>
+      </c>
+      <c r="U783" s="2" t="n">
+        <v>115.0</v>
+      </c>
+      <c r="V783" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W783" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X783" s="2" t="inlineStr">
+        <is>
+          <t>242177</t>
+        </is>
+      </c>
+      <c r="Y783" s="5" t="n">
+        <v>46322.0</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="2" t="inlineStr">
+        <is>
+          <t>FS777</t>
+        </is>
+      </c>
+      <c r="B784" s="2" t="inlineStr">
+        <is>
+          <t>510492000001631059</t>
+        </is>
+      </c>
+      <c r="C784" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D784" s="2" t="inlineStr">
+        <is>
+          <t>510492000000123277</t>
+        </is>
+      </c>
+      <c r="E784" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F784" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G784" s="2" t="inlineStr">
+        <is>
+          <t>238.800</t>
+        </is>
+      </c>
+      <c r="H784" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I784" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J784" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K784" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L784" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M784" s="2" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="N784" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Shoes Limited</t>
+        </is>
+      </c>
+      <c r="O784" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P784" s="5" t="n">
+        <v>46322.0</v>
+      </c>
+      <c r="Q784" s="6" t="n">
+        <v>46323.63145833334</v>
+      </c>
+      <c r="R784" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S784" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T784" s="2" t="inlineStr">
+        <is>
+          <t>510492000001631063</t>
+        </is>
+      </c>
+      <c r="U784" s="2" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="V784" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W784" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X784" s="2" t="inlineStr">
+        <is>
+          <t>242035</t>
+        </is>
+      </c>
+      <c r="Y784" s="5" t="n">
+        <v>46235.0</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="2" t="inlineStr">
+        <is>
+          <t>FS778</t>
+        </is>
+      </c>
+      <c r="B785" s="2" t="inlineStr">
+        <is>
+          <t>510492000001631078</t>
+        </is>
+      </c>
+      <c r="C785" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D785" s="2" t="inlineStr">
+        <is>
+          <t>510492000000123277</t>
+        </is>
+      </c>
+      <c r="E785" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F785" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G785" s="2" t="inlineStr">
+        <is>
+          <t>240.000</t>
+        </is>
+      </c>
+      <c r="H785" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I785" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J785" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K785" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L785" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M785" s="2" t="inlineStr">
+        <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="N785" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Shoes Limited</t>
+        </is>
+      </c>
+      <c r="O785" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P785" s="5" t="n">
+        <v>46322.0</v>
+      </c>
+      <c r="Q785" s="6" t="n">
+        <v>46323.63164351852</v>
+      </c>
+      <c r="R785" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S785" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T785" s="2" t="inlineStr">
+        <is>
+          <t>510492000001631082</t>
+        </is>
+      </c>
+      <c r="U785" s="2" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="V785" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W785" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X785" s="2" t="inlineStr">
+        <is>
+          <t>242053</t>
+        </is>
+      </c>
+      <c r="Y785" s="5" t="n">
+        <v>46235.0</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="2" t="inlineStr">
+        <is>
+          <t>FS780</t>
+        </is>
+      </c>
+      <c r="B786" s="2" t="inlineStr">
+        <is>
+          <t>510492000001631116</t>
+        </is>
+      </c>
+      <c r="C786" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D786" s="2" t="inlineStr">
+        <is>
+          <t>510492000000123277</t>
+        </is>
+      </c>
+      <c r="E786" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F786" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G786" s="2" t="inlineStr">
+        <is>
+          <t>238.800</t>
+        </is>
+      </c>
+      <c r="H786" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I786" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J786" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K786" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L786" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M786" s="2" t="inlineStr">
+        <is>
+          <t>780</t>
+        </is>
+      </c>
+      <c r="N786" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Shoes Limited</t>
+        </is>
+      </c>
+      <c r="O786" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P786" s="5" t="n">
+        <v>46322.0</v>
+      </c>
+      <c r="Q786" s="6" t="n">
+        <v>46323.63263888889</v>
+      </c>
+      <c r="R786" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S786" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T786" s="2" t="inlineStr">
+        <is>
+          <t>510492000001631120</t>
+        </is>
+      </c>
+      <c r="U786" s="2" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="V786" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W786" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X786" s="2" t="inlineStr">
+        <is>
+          <t>242088</t>
+        </is>
+      </c>
+      <c r="Y786" s="5" t="n">
+        <v>46266.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Customer_Payment_zoho.xlsx
+++ b/Customer_Payment_zoho.xlsx
@@ -86,7 +86,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y786"/>
+  <dimension ref="A1:Y788"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.53125" customWidth="true"/>
@@ -92190,6 +92190,240 @@
         <v>46266.0</v>
       </c>
     </row>
+    <row r="787">
+      <c r="A787" s="2" t="inlineStr">
+        <is>
+          <t>FS781</t>
+        </is>
+      </c>
+      <c r="B787" s="2" t="inlineStr">
+        <is>
+          <t>510492000001636002</t>
+        </is>
+      </c>
+      <c r="C787" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D787" s="2" t="inlineStr">
+        <is>
+          <t>510492000001025001</t>
+        </is>
+      </c>
+      <c r="E787" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F787" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G787" s="2" t="inlineStr">
+        <is>
+          <t>354.000</t>
+        </is>
+      </c>
+      <c r="H787" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I787" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J787" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K787" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L787" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M787" s="2" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="N787" s="2" t="inlineStr">
+        <is>
+          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
+        </is>
+      </c>
+      <c r="O787" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P787" s="5" t="n">
+        <v>46323.0</v>
+      </c>
+      <c r="Q787" s="6" t="n">
+        <v>46325.743472222224</v>
+      </c>
+      <c r="R787" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S787" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T787" s="2" t="inlineStr">
+        <is>
+          <t>510492000001636006</t>
+        </is>
+      </c>
+      <c r="U787" s="2" t="n">
+        <v>354.0</v>
+      </c>
+      <c r="V787" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W787" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X787" s="2" t="inlineStr">
+        <is>
+          <t>242170</t>
+        </is>
+      </c>
+      <c r="Y787" s="5" t="n">
+        <v>46303.0</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="2" t="inlineStr">
+        <is>
+          <t>FS782</t>
+        </is>
+      </c>
+      <c r="B788" s="2" t="inlineStr">
+        <is>
+          <t>510492000001636021</t>
+        </is>
+      </c>
+      <c r="C788" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D788" s="2" t="inlineStr">
+        <is>
+          <t>510492000001610001</t>
+        </is>
+      </c>
+      <c r="E788" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F788" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G788" s="2" t="inlineStr">
+        <is>
+          <t>240.000</t>
+        </is>
+      </c>
+      <c r="H788" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I788" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J788" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K788" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L788" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M788" s="2" t="inlineStr">
+        <is>
+          <t>782</t>
+        </is>
+      </c>
+      <c r="N788" s="2" t="inlineStr">
+        <is>
+          <t>UK Admission Manchester</t>
+        </is>
+      </c>
+      <c r="O788" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P788" s="5" t="n">
+        <v>46325.0</v>
+      </c>
+      <c r="Q788" s="6" t="n">
+        <v>46325.7487962963</v>
+      </c>
+      <c r="R788" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S788" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T788" s="2" t="inlineStr">
+        <is>
+          <t>510492000001636025</t>
+        </is>
+      </c>
+      <c r="U788" s="2" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="V788" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W788" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X788" s="2" t="inlineStr">
+        <is>
+          <t>242172</t>
+        </is>
+      </c>
+      <c r="Y788" s="5" t="n">
+        <v>46315.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
